--- a/test_doc/new_org/syllabus_7_social_studies.xlsx
+++ b/test_doc/new_org/syllabus_7_social_studies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>History: Tracing Changes Through a Thousand Years</t>
+          <t>Civics: Understanding Diversity</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New maps and sources</t>
+          <t>Diversity around us</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -461,22 +461,22 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Time and periods</t>
+          <t>Unity in diversity</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>History: New Kings and Kingdoms</t>
+          <t>History: The Mughal Empire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emergence of dynasties</t>
+          <t>Mughal rulers</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -491,7 +491,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warfare and forts</t>
+          <t>Mansabdars and jagirs</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -501,12 +501,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Geography: Environment</t>
+          <t>Geography: Maps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Components of environment</t>
+          <t>Kinds of maps</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Human environment</t>
+          <t>Map reading</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -531,16 +531,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Geography: Inside Our Earth</t>
+          <t>Civics: Government</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Layers of the earth</t>
+          <t>Levels of government</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,22 +551,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rocks and minerals</t>
+          <t>Democratic government</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Civics: On Equality</t>
+          <t>History: The Delhi Sultans</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equal right to vote</t>
+          <t>Rulers of Delhi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -574,33 +574,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Term 1</t>
+          <t>Term 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Struggles for equality</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>History: The Delhi Sultans</t>
+          <t>Geography: Inside Our Earth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rulers of Delhi</t>
+          <t>Layers of the earth</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,22 +611,22 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Rocks and minerals</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geography: Our Changing Earth</t>
+          <t>The Environment</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Earth movements</t>
+          <t>Pollution</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -641,26 +641,26 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Work of rivers and wind</t>
+          <t>Protecting nature</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Civics: Role of the Government in Health</t>
+          <t>History: New Kings and Kingdoms</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Public and private health</t>
+          <t>Emergence of dynasties</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -671,101 +671,11 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Healthcare for all</t>
+          <t>Warfare and forts</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>History: The Mughal Empire</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mughal rulers</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
         <v>4</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Mansabdars and jagirs</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Geography: Air</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Composition of atmosphere</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Weather instruments</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Civics: How the State Government Works</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MLAs and assemblies</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>The executive</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
